--- a/output/pdf_financials_xlsx/ACU.xlsx
+++ b/output/pdf_financials_xlsx/ACU.xlsx
@@ -790,10 +790,10 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000131</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004108</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1317,10 +1317,10 @@
         <v>-1.619633</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.424375</v>
+        <v>-1.424244</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.737822</v>
+        <v>-0.733714</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>-2.258461</v>
@@ -1383,10 +1383,10 @@
         <v>-1.615916</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.419952</v>
+        <v>-1.419821</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.737822</v>
+        <v>-0.733714</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>-2.258461</v>
@@ -1418,10 +1418,10 @@
         <v>-2951.013550531429</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-100.3801141685665</v>
+        <v>-100.3708534365446</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-29.42179013773358</v>
+        <v>-29.25797730227216</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>-515.2292393364984</v>
@@ -1529,13 +1529,13 @@
         <v>2.00496</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.833548</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>1.01557</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.821146</v>
       </c>
       <c r="I34" s="1" t="inlineStr">
         <is>
@@ -1595,13 +1595,13 @@
         <v>2.00496</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.833548</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>1.01557</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.821146</v>
       </c>
       <c r="I36" s="1" t="inlineStr">
         <is>
@@ -1991,13 +1991,13 @@
         <v>0.022804</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.035734</v>
+        <v>0.202186</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.08542</v>
+        <v>0.06985</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.877135</v>
+        <v>0.055989</v>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">

--- a/output/pdf_financials_xlsx/ACU.xlsx
+++ b/output/pdf_financials_xlsx/ACU.xlsx
@@ -626,7 +626,7 @@
         <v>0.720059</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.785164</v>
+        <v>0.815164</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012441</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -4118,13 +4118,13 @@
         <v>0</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.048055</v>
       </c>
       <c r="G111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.059184</v>
       </c>
       <c r="I111" s="1" t="inlineStr">
         <is>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012441</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -4905,13 +4905,13 @@
         <v>0</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.048055</v>
       </c>
       <c r="G134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.059184</v>
       </c>
       <c r="I134" s="1" t="inlineStr">
         <is>
@@ -4926,7 +4926,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.366649</v>
+        <v>-1.37909</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-1.533663</v>
@@ -4938,7 +4938,7 @@
         <v>-0.650159</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-1.533009</v>
+        <v>-1.581064</v>
       </c>
       <c r="G135" s="3" t="n">
         <v>-1.514403</v>
@@ -9582,7 +9582,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -9692,7 +9696,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -10624,7 +10632,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -11774,7 +11786,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E127" s="5" t="n">
         <v>1.320507</v>
       </c>
@@ -12040,7 +12056,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E132" s="5" t="n">
         <v>-0.012441</v>
       </c>
@@ -14912,7 +14932,11 @@
           <t>Directors fees (14)</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
